--- a/AAII_Financials/Quarterly/DE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>DE</t>
   </si>
@@ -656,516 +656,528 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="2">
         <v>46145</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46054</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45963</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45774</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45683</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45501</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45410</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45319</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44955</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44864</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44682</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44591</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44409</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44318</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44136</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44045</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43954</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43863</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43772</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43674</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43583</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43492</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43401</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43219</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43128</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43037</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42946</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42764</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12608000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13369000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9611000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12338000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12018000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12763000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8508000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10960000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13152000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15235000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12185000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15383000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15801000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17387000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12652000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15536000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14102000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13044000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9569000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11327000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11500000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12058000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9112000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9731000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8925000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9273000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7635000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9896000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10042000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11349400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7993600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9415900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10308300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10720000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6913500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>8017700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7807800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>8287000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5625200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6519600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8049000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8266000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6280000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7944000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7562000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7609000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5037000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6565000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7813000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9157000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7200000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9427000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9624000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10730000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7844000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10205000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9506000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8841000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6605000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7809000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7574000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7928000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5813000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6401000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5821000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6312000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5049000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6719000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6862000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8206200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5797900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6847000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7632700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7878200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4783500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>5893100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>5354000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>5824800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4041700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>4379600</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3307000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3854000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2133000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3100000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3171000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3828000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2167000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2934000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3875000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4701000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3692000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4620000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5020000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5404000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4808000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5331000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4596000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4203000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2964000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3518000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3926000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4130000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3299000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3330000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3104000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2961000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2586000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3177000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3180000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3143200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2195700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2568900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2675600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2841800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2130000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2124600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2453800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2462200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1583500</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2140000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,130 +1220,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E12" s="3">
         <v>583000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>554000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>680000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>556000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>549000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>526000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>619000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>541000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>565000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>533000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>606000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>528000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>547000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>495000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>576000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>481000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>453000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>402000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>450000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>394000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>377000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>366000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>406000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>370000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>403000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>410000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>488000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>431000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>457100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>406800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>469900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>415700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>415200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>356800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>397000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>335400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>325400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>312100</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>386000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1452,94 +1468,97 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>24</v>
+      <c r="D14" s="3">
+        <v>-110000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="3">
         <v>95000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>61000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-32000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-25000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>120000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="3">
         <v>18000</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>173000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>90000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>94000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>90000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>24</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>301000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>40000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>102000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>126000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>77000</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>24</v>
@@ -1547,8 +1566,8 @@
       <c r="AG14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1574,53 +1593,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>603000</v>
+      </c>
+      <c r="E15" s="3">
         <v>594000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>590000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>334000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>564000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>555000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>549000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>340000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>553000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>525000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>520000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>333000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>532000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>501000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1696,8 +1718,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,252 +1762,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10922000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11013000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8720000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10810000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10204000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10395000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7550000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9598000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10666000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12062000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9930000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12332000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12052000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13337000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9680000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12302000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11267000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10631000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8189000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9504000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9133000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9478000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7313000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8313000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7365000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8239000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6736000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8675000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8529000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9610200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6968400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8215400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8961100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9232600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5845300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>7130900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6480600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6933800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5021100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5882400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1686000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2356000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>891000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1528000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1814000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2368000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>958000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1362000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2486000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3173000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2255000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3051000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3749000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4050000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2972000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3234000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2835000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2413000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1380000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1823000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2367000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2580000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1799000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1418000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1560000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1034000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>899000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1221000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1513000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1739200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1025200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1200500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1347200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1487400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1068200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>886800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1327200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1353200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>604100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>637200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2025,53 +2057,54 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-159000</v>
+      </c>
+      <c r="E20" s="3">
         <v>5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-15000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>30000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>69000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-19000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-18000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2000</v>
       </c>
       <c r="M20" s="3">
         <v>-2000</v>
       </c>
       <c r="N20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="O20" s="3">
         <v>-37000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>140000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2079,564 +2112,579 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>326000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>27000</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>652000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>104000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-389000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>160000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>216000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>130000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>79000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>121000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>77000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-395000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>61000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-190000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>93000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-267900</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-115000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2448000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2945000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1496000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1832000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2309000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2926000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1506000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1721000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3057000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3700000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2777000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3421000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4141000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4553000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3466000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3686000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3345000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3186000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1866000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2304000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2909000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3096000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2337000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1898000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2107000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2215000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1541000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1329000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2178500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2468400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1658500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1761500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1962400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2052000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1136400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1384300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1573100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1873600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>751900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>923600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E22" s="3">
         <v>63000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>55000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>45000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>74000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>63000</v>
       </c>
       <c r="I22" s="3">
         <v>63000</v>
       </c>
       <c r="J22" s="3">
+        <v>63000</v>
+      </c>
+      <c r="K22" s="3">
         <v>42000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>56000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>40000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>29000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>479000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>349000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>296000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>187000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>229000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>210000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>244000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>268000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>271000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>278000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>290000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>758000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>434000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>560000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>481800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>478000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>300600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>278100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>180700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>155300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>181200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>247300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>276900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>8200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>87800</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1906000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2288000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>851000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1414000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1610000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2340000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>894000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1491000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2356000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3119000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2217000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3075000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3608000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3850000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2493000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2885000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2539000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2552000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1151000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1613000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2150000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2312000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1528000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1116000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1270000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>928000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>569000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>825000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1113000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1473400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>677200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>978900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1190100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1383700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>517900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>766600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>889900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1169300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>328000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>434400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>529000</v>
+      </c>
+      <c r="E24" s="3">
         <v>518000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>196000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>354000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>339000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>539000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>249000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>625000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>751000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>469000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>707000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>636000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>991000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>537000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>643000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>654000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>461000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>250000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>330000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>491000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>530000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>308000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>330000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>457000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>245000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>145000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>248000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>343500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>184100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>240500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>350700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>351100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>80300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>222400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>253200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>365800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>129200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>140200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2757,252 +2805,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1377000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1770000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>655000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1060000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1271000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1801000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>867000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1242000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1731000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2368000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1748000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2368000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2972000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2859000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1956000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2242000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1885000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2091000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>901000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1283000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1659000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1782000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1220000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>786000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>813000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>683000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>519000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>680000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>865000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1129900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>493100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>738400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>839400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1032600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>437600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>544200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>636700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>803500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>198800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>294200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1773000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>656000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1065000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1289000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1804000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>869000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1245000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1734000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2370000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1751000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2369000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2978000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2860000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1959000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2246000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1884000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2098000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>903000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1283000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1667000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1790000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1224000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>758000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>811000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>666000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>517000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>680000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>872000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1134900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>498400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>747700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>848200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1034100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>442100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>510100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>641600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>809300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>198900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>285200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3123,8 +3180,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3188,8 +3248,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -3206,32 +3266,32 @@
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="3">
         <v>41000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>27000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI29" s="3">
         <v>37000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>62000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>174000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-977200</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3245,8 +3305,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3367,8 +3430,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3489,53 +3555,56 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>15000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-30000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-69000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>19000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>18000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2000</v>
       </c>
       <c r="M32" s="3">
         <v>2000</v>
       </c>
       <c r="N32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O32" s="3">
         <v>37000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-140000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3543,198 +3612,204 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-326000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-27000</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>24000</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-652000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-104000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>389000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-160000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-216000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-130000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-79000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-121000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-77000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>395000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-61000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>190000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-93000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>267900</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>115000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1773000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>656000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1065000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1289000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1804000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>869000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1245000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1734000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2370000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1751000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2369000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2978000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2860000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1959000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2246000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1884000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2098000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>903000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1283000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1667000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1790000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1224000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>758000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>811000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>666000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>517000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>721000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>899000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1134900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>498400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>784700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>910200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1208100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-535100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>510100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>641600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>809300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>198900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>285200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3855,257 +3930,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1773000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>656000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1065000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1289000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1804000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>869000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1245000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1734000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2370000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1751000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2369000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2978000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2860000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1959000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2246000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1884000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2098000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>903000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1283000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1667000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1790000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1224000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>758000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>811000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>666000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>517000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>721000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>899000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1134900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>498400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>784700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>910200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1208100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-535100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>510100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>641600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>809300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>198900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>285200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E38" s="2">
         <v>46145</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46054</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45963</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45774</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45683</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45501</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45410</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45319</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44955</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44864</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44682</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44591</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44409</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44318</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44136</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44045</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43954</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43863</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43772</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43674</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43583</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43492</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43401</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43219</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43128</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43037</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42946</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42764</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4148,8 +4232,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4192,175 +4277,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6607000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5917000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4769000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6340000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6641000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6331000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4840000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5615000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5385000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3800000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3467000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5720000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4858000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3587000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3976000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4774000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4359000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3878000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4472000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8017000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7519000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7182000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6962000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7066000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8190000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8900000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3602000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3857000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3383000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3483700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3625700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3904000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3923300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4201400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3915100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>9334900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6537400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4525800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3890000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>4335800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E42" s="3">
         <v>433000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>486000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>564000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>585000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>531000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>249000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>387000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>417000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>303000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>361000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>321000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>276000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>290000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4436,297 +4525,306 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10297000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10256000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8509000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7737000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9014000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9807000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7990000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7697000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9823000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11495000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9884000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9759000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12475000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12619000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14690000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14838000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13836000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12637000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10307000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10632000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12371000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11769000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>10137000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10125000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12185000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>11915000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>11243000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11146000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>13547000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>13844700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11747300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>10782900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>12197500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>12379900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>10228400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9319600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>10170600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9730300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8392400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>9172800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7811000</v>
+      </c>
+      <c r="E44" s="3">
         <v>8188000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>8286000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7406000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7713000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7870000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7744000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7093000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7696000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8443000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8937000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8160000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9350000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9713000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10056000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8495000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>9121000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>9030000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7935000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6781000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6410000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6042000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5956000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4999000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5650000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6171000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6482000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5975000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6747000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>7160900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>7401900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>6148900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>6239300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>6888900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>6614200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3904100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4252900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4114800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>3959600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>3340500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>118000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>81000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>349000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>99000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>742000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>91000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4802,53 +4900,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>77883000</v>
+      </c>
+      <c r="E46" s="3">
         <v>77192000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74100000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>77128000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>79144000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>78272000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>76457000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>80206000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>81256000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>79410000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75546000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>78555000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>78011000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>73500000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4924,34 +5025,37 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E47" s="3">
         <v>409000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>389000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>510000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>395000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>372000</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>122000</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>24</v>
@@ -4959,339 +5063,348 @@
       <c r="M47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O47" s="3">
         <v>126000</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R47" s="3">
         <v>37734000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>37368000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>35775000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>34767000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>34102000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>34702000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>32325000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>31844000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>30283000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>30584000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>28653000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>28074000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>28120000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>29991000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>27833000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>26650200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>25884900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>27751500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>25899900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>24956900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>24511400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>25738200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>24369000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>24063100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>23697300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>24388400</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7975000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8004000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8053000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8396000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7680000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7523000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7392000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7854000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7058000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6999000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6879000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7162000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6385000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6254000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12714000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12679000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12220000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12180000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12565000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13099000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12941000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13157000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13098000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13439000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13253000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13271000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13780000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13540000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13067000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12797000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12688800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13032900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12443400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12466000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12401000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>11661400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>11204100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>10883800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>10855700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>16973600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5406000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5488000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5160000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5550000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5135000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5058000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4809000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5462000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4990000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5000000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5078000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5483000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5193000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5185000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5146000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4905000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5035000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5164000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4401000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4566000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4415000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4500000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4536000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4408000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4285000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4228000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4294000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4297000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4457000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4500800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4555100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4663100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4627300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4880900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4771300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1251300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>937800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>897000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>904700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>919800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5412,8 +5525,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5534,130 +5650,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6129000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6002000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5923000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4111000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5709000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5622000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5419000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3727000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5487000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5283000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5249000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3604000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5706000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5473000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4909000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4554000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4235000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4163000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4178000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4746000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2877000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2774000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2564000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2362000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2565000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2395000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2314000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2306000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2519000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2421600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2182300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2106300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2382200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2336400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2456500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2953200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>3286800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>3218100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>3097100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>3058000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5778,130 +5900,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>107607000</v>
+      </c>
+      <c r="E54" s="3">
         <v>107001000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>103436000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>105996000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107817000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106303000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103119000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>107320000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>107841000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>105628000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>101371000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>104087000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>103397000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>98347000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>91620000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>90030000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>86817000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>84099000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>79614000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>84114000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>80688000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>78979000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>75480000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>75091000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>77264000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>77326000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>71821000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>73011000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>73530000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>72729600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>69918200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>70108000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>69390100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>69873000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>66577500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>65786300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>62349900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>58968800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>56296600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>57918500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5944,8 +6072,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5988,299 +6117,306 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3473000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3545000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3234000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3186000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2938000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3021000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2608000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2908000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2757000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3160000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3373000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3626000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3485000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3820000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5668000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14822000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12986000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12679000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10384000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12069000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10903000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10354000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9208000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9912000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9327000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8645000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8315000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9659000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9610300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8932500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9840900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9209500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9564300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8233700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>8380900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>7496800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>7186500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>6259200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>14489800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23608000</v>
+      </c>
+      <c r="E58" s="3">
         <v>21924000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21036000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20858000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22682000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24017000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21532000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>22526000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23729000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>25642000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>23924000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>26010000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24617000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>23204000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>18993000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>18303000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>19096000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>16419000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>14472000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15524000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15681000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>14017000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>13193000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>13264000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>14436000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15819000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>14424000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15105000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>16190000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>16464000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>15201500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>15018700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>15532200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>15295700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>14171800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>14154000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>13800300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>12188200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>11661800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>18820700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6113000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6324000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6212000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6051000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6276000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6248000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6012000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6350000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7690000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7603000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5775000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6313000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6000000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5886000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6839000</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>24</v>
@@ -6288,35 +6424,35 @@
       <c r="T59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V59" s="3">
         <v>267000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>279000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>304000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>328000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>315000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>305000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>318000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>319000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>361000</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>24</v>
@@ -6330,8 +6466,8 @@
       <c r="AH59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
+      <c r="AI59" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AJ59" s="3">
         <v>0</v>
@@ -6354,53 +6490,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36534000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34874000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32888000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34097000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35514000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36575000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34543000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38064000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39105000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>39014000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36301000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40783000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38783000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36910000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6476,130 +6615,136 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9251000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9197000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9217000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8960000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9074000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8965000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8781000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6873000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6850000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6845000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7563000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7491000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7607000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7604000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>35071000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33596000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32132000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32447000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32838000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32888000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>32280000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>33346000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>32772000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32734000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>34037000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>34324000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>30475000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>30229000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>29242000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28255400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>27855200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>27237400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>26838000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>26278600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>26421800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>25891300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>23674300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>23253100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>22916600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>23703000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6642,86 +6787,89 @@
       <c r="P62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R62" s="3">
         <v>3012000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2952000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3472000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3548000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3845000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4920000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5787000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5838000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5906000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5932000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6255000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6155000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6201000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6448000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6288000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6246600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6284300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6306800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7046500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>7928800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>8097300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7627600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>8609600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>8502200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>8439300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>8440500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6842,8 +6990,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6964,8 +7115,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7086,130 +7240,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79566000</v>
+      </c>
+      <c r="E66" s="3">
         <v>79541000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>77079000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>79989000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>82553000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>81925000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80555000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>84395000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>84692000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82842000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>79192000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>82201000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>80245000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>75846000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>70288000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>69768000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>67784000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>65195000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>61810000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>65683000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>64957000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>63887000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>61397000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>62154000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>64376000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>65462000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>59895000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>61598000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>61264000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>60810100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>58590400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>58820200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>59033800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>59462700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>57324900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>56229000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>53777700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>51284100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>49471100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>51398500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7252,8 +7412,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7374,8 +7535,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7496,8 +7660,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7618,8 +7785,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7740,130 +7910,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>62169000</v>
+      </c>
+      <c r="E72" s="3">
         <v>61228000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59895000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>59676000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>59023000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58191000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56829000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56402000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>55559000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>54228000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52266000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>50931000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>48947000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46336000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>43846000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>42247000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40346000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38805000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37029000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>36449000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>35491000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>34105000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>32596000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31646000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31128000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>30556000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>30129000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>29852000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>29369000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>28708800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>27816300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>27553000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>26272300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>25586000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>24571900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>25301300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>24984200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>24524400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>23914300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>23911300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7984,8 +8160,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8106,8 +8285,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8228,130 +8410,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27990000</v>
+      </c>
+      <c r="E76" s="3">
         <v>27406000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26300000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25950000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25175000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24287000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22479000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22836000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23062000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22684000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22075000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21785000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23048000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22395000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21332000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20262000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19033000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18904000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17804000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18431000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15731000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15092000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14083000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12937000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12888000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11864000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11926000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11413000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12266000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11919500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11327800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11287800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10356300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10410300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9252600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9557300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>8572200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7684700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6825500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6520000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8472,257 +8660,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E80" s="2">
         <v>46145</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46054</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45963</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45774</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45683</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45501</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45410</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45319</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44955</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44864</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44682</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44591</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44409</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44318</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44136</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44045</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43954</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43863</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43772</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43674</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43583</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43492</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43401</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43219</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43128</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43037</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42946</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42764</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1379000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1773000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>656000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1065000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1289000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1804000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>869000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1245000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1734000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2370000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1751000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2369000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2978000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2860000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1959000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2246000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1884000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2098000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>903000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1283000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1667000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1790000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1224000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>758000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>811000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>666000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>517000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>721000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>899000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1134900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>498400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>784700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>910200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1208100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-535100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>510100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>641600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>809300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>198900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>285200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8765,130 +8962,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>532000</v>
+      </c>
+      <c r="E83" s="3">
         <v>518000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>508000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>298000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>512000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>484000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>478000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>290000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>490000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>456000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>455000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>294000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>490000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>391000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>494000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>452000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>510000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>447000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>486000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>481000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>515000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>516000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>538000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>504000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>547000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>529000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>538000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>497000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>505500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>513200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>503300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>482100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>494200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>487600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>463200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>436500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>435900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>427400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>415700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>401400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9009,8 +9210,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9131,8 +9335,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9253,8 +9460,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9375,8 +9585,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9497,130 +9710,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1932000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-890000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3995000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2896000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1700000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1132000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5092000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3195000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1852000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-908000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5693000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3043000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1099000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1246000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4281000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2180000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>791000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2553000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3412000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2528000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1643000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>143000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3426000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3281000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1284000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-508000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3008000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1898800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>155900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1650700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2494000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>548100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>75900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1296000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1470500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>893000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>573000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-736700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2449800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9663,130 +9882,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-903000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1058000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-688000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1367000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1052000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1018000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-791000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1594000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1120000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1272000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-816000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1613000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1042000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1001000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-812000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1475000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-963000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-766000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-584000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-878000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-618000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-166000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-154000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-226000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-153000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-170000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-271000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-364000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-265100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-193500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-297400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-325400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-218400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-175900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-176300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-221200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-120700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1280600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1075600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-3792600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9907,8 +10130,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10029,130 +10255,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-918000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1822000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1256000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1580000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-637000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1416000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2793000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2001000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2887000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1217000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4186000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3069000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2254000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>760000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4055000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2542000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2536000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>648000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2648000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1715000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1966000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>579000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1547000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-996000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1795000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1756800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1340800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>968600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1689400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1062700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4090300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1343100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-601700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-803900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>1104400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-814800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10195,130 +10427,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E96" s="3">
         <v>437000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>441000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>438000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>439000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>440000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>403000</v>
       </c>
       <c r="J96" s="3">
         <v>403000</v>
       </c>
       <c r="K96" s="3">
+        <v>403000</v>
+      </c>
+      <c r="L96" s="3">
         <v>406000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>410000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>386000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>362000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>368000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>356000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-341000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-342000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-322000</v>
       </c>
       <c r="T96" s="3">
         <v>-322000</v>
       </c>
       <c r="U96" s="3">
+        <v>-322000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-327000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-279000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-281000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-238000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-242000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-238000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-239000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-242000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-240000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-240700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-242000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-220300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-223200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-195700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-193900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-193000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-192700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-191800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-190600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-188900</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-188700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10439,8 +10675,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10561,8 +10800,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10683,370 +10925,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E100" s="3">
         <v>863000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2490000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3022000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-736000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>102000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-923000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1928000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>373000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1483000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2645000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-571000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1362000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2356000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-339000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>311000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>901000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1191000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1577000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-227000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-410000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>492000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-933000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2704000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2619000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5106000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-763000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-707000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-256200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1069400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>402800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-779600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>560700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1326300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-231000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2630500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1584000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>840500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-768500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1594400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E101" s="3">
         <v>107000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-87000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-31000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-21000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>16000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-94000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>55000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>62000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-81000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-33000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>62000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-81000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-33000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-36000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-74000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-51000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-45000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>48000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>103000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-48000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>182000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-101000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-32000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>10800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-21900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-45300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-73800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-52700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>198600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>39600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>125000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>31800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-39300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-20400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1015000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1062000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1460000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-314000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>668000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1272000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-726000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>340000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1566000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>427000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2320000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>842000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1391000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1209000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-763000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>456000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>506000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-590000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3556000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>486000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>358000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>217000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-108000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1128000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-703000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5293000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-246000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>474000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-103400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-137400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-292200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-19300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-278100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>286300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-5419800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>2797500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>2011600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>635800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-445800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>14800</v>
       </c>
     </row>
